--- a/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/miRNA Experiment/GDC_Exp_miRNA_DM.xlsx
+++ b/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/miRNA Experiment/GDC_Exp_miRNA_DM.xlsx
@@ -1,26 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjohnson/Projects/SDD-Dataset/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/miRNA Experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3248845-D378-1C40-8E27-2FA18C6F6D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24A9C36-39BB-4443-BE5D-01383BAA3510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12380" yWindow="8000" windowWidth="27240" windowHeight="16440"/>
+    <workbookView xWindow="28060" yWindow="2240" windowWidth="21600" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GDC_Exp_miRNA_DM" sheetId="1" r:id="rId1"/>
+    <sheet name="InfoSheet" sheetId="2" r:id="rId1"/>
+    <sheet name="Prefixes" sheetId="4" r:id="rId2"/>
+    <sheet name="Mapping Process" sheetId="3" r:id="rId3"/>
+    <sheet name="Timeline" sheetId="5" r:id="rId4"/>
+    <sheet name="New Concepts" sheetId="6" r:id="rId5"/>
+    <sheet name="Codebook" sheetId="7" r:id="rId6"/>
+    <sheet name="Dictionary Mapping" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t>Column</t>
   </si>
@@ -79,18 +85,12 @@
     <t>miRNA_ID</t>
   </si>
   <si>
-    <t>sio:Identifier</t>
-  </si>
-  <si>
     <t>??gene</t>
   </si>
   <si>
     <t>read_count</t>
   </si>
   <si>
-    <t>sio:Count, stato:0000064</t>
-  </si>
-  <si>
     <t>??gene_expression_value</t>
   </si>
   <si>
@@ -100,80 +100,74 @@
     <t>reads_per_million_miRNA_mapped</t>
   </si>
   <si>
-    <t>sio:Ratio</t>
-  </si>
-  <si>
     <t>counts normalized to reads per million mapped reads (RPM)</t>
   </si>
   <si>
-    <t>cross-mapped</t>
-  </si>
-  <si>
-    <t>xsd:boolean</t>
-  </si>
-  <si>
-    <t>??overlap</t>
-  </si>
-  <si>
-    <t>it's a phenomenon of mi-RNA parts exchanging</t>
-  </si>
-  <si>
-    <t>ncit:C45254</t>
-  </si>
-  <si>
-    <t>isoform_coords</t>
-  </si>
-  <si>
-    <t>sio:Coordinate</t>
-  </si>
-  <si>
-    <t>??isoform</t>
-  </si>
-  <si>
-    <t>miRNA_region</t>
-  </si>
-  <si>
-    <t>sio:SpatialRegion</t>
-  </si>
-  <si>
     <t>??subject</t>
   </si>
   <si>
-    <t>sio:Human</t>
-  </si>
-  <si>
-    <t>sio:SubjectRole</t>
-  </si>
-  <si>
     <t>??study</t>
   </si>
   <si>
     <t>microRNA</t>
   </si>
   <si>
-    <t>sio:GeneExpressionValue</t>
-  </si>
-  <si>
-    <t>sio:Overlap</t>
-  </si>
-  <si>
-    <t>sio:Gene</t>
-  </si>
-  <si>
-    <t>sio:isPartOf</t>
-  </si>
-  <si>
     <t>hasco:Study</t>
   </si>
   <si>
-    <t>heals:Isoform</t>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>sio</t>
+  </si>
+  <si>
+    <t>http://semanticscience.org/resource/</t>
+  </si>
+  <si>
+    <t>stato</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/STATO_</t>
+  </si>
+  <si>
+    <t>hasco</t>
+  </si>
+  <si>
+    <t>http://hadatac.org/ont/hasco/</t>
+  </si>
+  <si>
+    <t>sio:SIO_000115</t>
+  </si>
+  <si>
+    <t>sio:SIO_000794, stato:0000064</t>
+  </si>
+  <si>
+    <t>sio:SIO_000068</t>
+  </si>
+  <si>
+    <t>sio:SIO_000883</t>
+  </si>
+  <si>
+    <t>sio:SIO_000485</t>
+  </si>
+  <si>
+    <t>sio:SIO_001018</t>
+  </si>
+  <si>
+    <t>sio:SIO_001077</t>
+  </si>
+  <si>
+    <t>sio:SIO_010035</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -308,6 +302,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -490,7 +505,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -605,8 +620,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -649,11 +679,16 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -687,6 +722,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1006,9 +1042,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99FDC419-DFFA-E54A-A020-46CBB09998E8}">
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60CFBF4A-8F92-534A-9527-C77D16BACE32}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{2B0D8E04-59A5-9740-8A04-9B70083C265F}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{9F885568-8448-7C43-A766-13E1ACF5A2BB}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{86A63C85-E4B4-6548-9494-F898C4810D90}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F114A9C2-A20F-8C40-BE9C-1C7A903612D1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992A241E-84AC-CE41-8030-CA1118FDC6AA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D65403-38E9-E54E-ACB7-7DC5EB38DF22}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3704FB72-8ED3-DE4A-98FD-5727EBDAD804}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1070,150 +1203,89 @@
       <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="Q3" t="s">
         <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
       </c>
       <c r="Q5" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
